--- a/sample_data/6月抖音投放.xlsx
+++ b/sample_data/6月抖音投放.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K321"/>
+  <dimension ref="A1:M321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,16 @@
           <t>录入日期</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,10 +489,8 @@
           <t>王伟磊</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>15121819600</t>
-        </is>
+      <c r="B2" t="n">
+        <v>15121819600</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -523,6 +531,14 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="L2" t="n">
+        <v>406.53</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -530,10 +546,8 @@
           <t>秦华文</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>13626542351</t>
-        </is>
+      <c r="B3" t="n">
+        <v>13626542351</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
@@ -574,6 +588,14 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="L3" t="n">
+        <v>519.5</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -581,10 +603,8 @@
           <t>吴秀</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>18995931034</t>
-        </is>
+      <c r="B4" t="n">
+        <v>18995931034</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -625,6 +645,14 @@
           <t>2024-04-17</t>
         </is>
       </c>
+      <c r="L4" t="n">
+        <v>524.64</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,10 +660,8 @@
           <t>秦桂平</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>13992832764</t>
-        </is>
+      <c r="B5" t="n">
+        <v>13992832764</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -676,6 +702,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -683,10 +717,8 @@
           <t>秦娜</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18853767242</t>
-        </is>
+      <c r="B6" t="n">
+        <v>18853767242</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -719,6 +751,14 @@
           <t>2024-03-11</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>443.89</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,10 +766,8 @@
           <t>姜娜敏</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>15026916697</t>
-        </is>
+      <c r="B7" t="n">
+        <v>15026916697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -774,6 +812,14 @@
           <t>2024-08-10</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>435.54</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -781,10 +827,8 @@
           <t>褚涛</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>13548281489</t>
-        </is>
+      <c r="B8" t="n">
+        <v>13548281489</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
@@ -825,6 +869,14 @@
           <t>2024-02-27</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>138.92</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -832,10 +884,8 @@
           <t>张华</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13839117182</t>
-        </is>
+      <c r="B9" t="n">
+        <v>13839117182</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
@@ -872,6 +922,14 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>755.04</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -879,10 +937,8 @@
           <t>蒋桂</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>18957871331</t>
-        </is>
+      <c r="B10" t="n">
+        <v>18957871331</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -923,6 +979,14 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>280.08</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -930,10 +994,8 @@
           <t>周超</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>18973829973</t>
-        </is>
+      <c r="B11" t="n">
+        <v>18973829973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -974,6 +1036,14 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>499.84</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -981,10 +1051,8 @@
           <t>李刚平</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>13906513338</t>
-        </is>
+      <c r="B12" t="n">
+        <v>13906513338</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1025,6 +1093,14 @@
           <t>2024-02-20</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1032,10 +1108,8 @@
           <t>李平伟</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>13932677360</t>
-        </is>
+      <c r="B13" t="n">
+        <v>13932677360</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
@@ -1072,6 +1146,14 @@
           <t>2024-10-11</t>
         </is>
       </c>
+      <c r="L13" t="n">
+        <v>666.54</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1079,10 +1161,8 @@
           <t>姜静</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>15109805009</t>
-        </is>
+      <c r="B14" t="n">
+        <v>15109805009</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1127,6 +1207,14 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="L14" t="n">
+        <v>629.64</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1134,10 +1222,8 @@
           <t>杨杰</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>18839909169</t>
-        </is>
+      <c r="B15" t="n">
+        <v>18839909169</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1182,6 +1268,14 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1189,10 +1283,8 @@
           <t>许涛</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>13610799118</t>
-        </is>
+      <c r="B16" t="n">
+        <v>13610799118</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
@@ -1233,6 +1325,14 @@
           <t>2024-08-12</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>634.88</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1240,10 +1340,8 @@
           <t>许霞华</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18980841241</t>
-        </is>
+      <c r="B17" t="n">
+        <v>18980841241</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1284,6 +1382,14 @@
           <t>2024-11-20</t>
         </is>
       </c>
+      <c r="L17" t="n">
+        <v>262.58</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1291,10 +1397,8 @@
           <t>朱超</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>13701640052</t>
-        </is>
+      <c r="B18" t="n">
+        <v>13701640052</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1335,6 +1439,14 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="L18" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1342,10 +1454,8 @@
           <t>陈秀</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>15898262045</t>
-        </is>
+      <c r="B19" t="n">
+        <v>15898262045</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1386,6 +1496,14 @@
           <t>2024-07-27</t>
         </is>
       </c>
+      <c r="L19" t="n">
+        <v>178.76</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1393,10 +1511,8 @@
           <t>陈磊华</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>13626025634</t>
-        </is>
+      <c r="B20" t="n">
+        <v>13626025634</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -1429,6 +1545,14 @@
           <t>2024-08-23</t>
         </is>
       </c>
+      <c r="L20" t="n">
+        <v>510.84</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1436,10 +1560,8 @@
           <t>施洋磊</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>15103654145</t>
-        </is>
+      <c r="B21" t="n">
+        <v>15103654145</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1480,6 +1602,14 @@
           <t>2024-01-20</t>
         </is>
       </c>
+      <c r="L21" t="n">
+        <v>722.62</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1487,10 +1617,8 @@
           <t>郑霞</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>13556981693</t>
-        </is>
+      <c r="B22" t="n">
+        <v>13556981693</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -1523,6 +1651,14 @@
           <t>2024-02-05</t>
         </is>
       </c>
+      <c r="L22" t="n">
+        <v>745.02</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1530,10 +1666,8 @@
           <t>吕霞</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>13714846564</t>
-        </is>
+      <c r="B23" t="n">
+        <v>13714846564</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1574,6 +1708,14 @@
           <t>2024-06-04</t>
         </is>
       </c>
+      <c r="L23" t="n">
+        <v>689.46</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1581,10 +1723,8 @@
           <t>尤强</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>18895777387</t>
-        </is>
+      <c r="B24" t="n">
+        <v>18895777387</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1625,6 +1765,14 @@
           <t>2024-12-10</t>
         </is>
       </c>
+      <c r="L24" t="n">
+        <v>231.73</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1632,10 +1780,8 @@
           <t>许磊静</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>13803791769</t>
-        </is>
+      <c r="B25" t="n">
+        <v>13803791769</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1668,6 +1814,14 @@
           <t>2024-01-03</t>
         </is>
       </c>
+      <c r="L25" t="n">
+        <v>139.92</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1675,10 +1829,8 @@
           <t>郑文</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>15087083172</t>
-        </is>
+      <c r="B26" t="n">
+        <v>15087083172</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1719,6 +1871,14 @@
           <t>2024-08-16</t>
         </is>
       </c>
+      <c r="L26" t="n">
+        <v>526.65</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1726,10 +1886,8 @@
           <t>褚英涛</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>15234873471</t>
-        </is>
+      <c r="B27" t="n">
+        <v>15234873471</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1774,6 +1932,14 @@
           <t>2024-12-21</t>
         </is>
       </c>
+      <c r="L27" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1781,10 +1947,8 @@
           <t>陈桂</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>15965876036</t>
-        </is>
+      <c r="B28" t="n">
+        <v>15965876036</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1825,6 +1989,14 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="L28" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1832,10 +2004,8 @@
           <t>孔娟英</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>18793734670</t>
-        </is>
+      <c r="B29" t="n">
+        <v>18793734670</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1880,6 +2050,14 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="L29" t="n">
+        <v>200.23</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1887,10 +2065,8 @@
           <t>钱娜静</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>13772046537</t>
-        </is>
+      <c r="B30" t="n">
+        <v>13772046537</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1935,6 +2111,14 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="L30" t="n">
+        <v>417.42</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1942,10 +2126,8 @@
           <t>李艳</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>13900330923</t>
-        </is>
+      <c r="B31" t="n">
+        <v>13900330923</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1982,6 +2164,14 @@
           <t>2024-03-26</t>
         </is>
       </c>
+      <c r="L31" t="n">
+        <v>195.69</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1989,10 +2179,8 @@
           <t>王文洋</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>13990496631</t>
-        </is>
+      <c r="B32" t="n">
+        <v>13990496631</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2037,6 +2225,14 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="L32" t="n">
+        <v>600.35</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2044,10 +2240,8 @@
           <t>张娜勇</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>13867165726</t>
-        </is>
+      <c r="B33" t="n">
+        <v>13867165726</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -2084,6 +2278,14 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="L33" t="n">
+        <v>118.04</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2091,10 +2293,8 @@
           <t>秦勇娜</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>15273799650</t>
-        </is>
+      <c r="B34" t="n">
+        <v>15273799650</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2135,6 +2335,14 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="L34" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2142,10 +2350,8 @@
           <t>秦秀</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>15113678377</t>
-        </is>
+      <c r="B35" t="n">
+        <v>15113678377</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2186,6 +2392,14 @@
           <t>2024-07-07</t>
         </is>
       </c>
+      <c r="L35" t="n">
+        <v>771.88</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2193,10 +2407,8 @@
           <t>陶秀娟</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>13585574443</t>
-        </is>
+      <c r="B36" t="n">
+        <v>13585574443</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
@@ -2233,6 +2445,14 @@
           <t>2024-09-04</t>
         </is>
       </c>
+      <c r="L36" t="n">
+        <v>616.42</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2240,10 +2460,8 @@
           <t>秦英文</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>18794134352</t>
-        </is>
+      <c r="B37" t="n">
+        <v>18794134352</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2284,6 +2502,14 @@
           <t>2024-11-22</t>
         </is>
       </c>
+      <c r="L37" t="n">
+        <v>585.1</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2291,10 +2517,8 @@
           <t>姜敏兰</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>15277752047</t>
-        </is>
+      <c r="B38" t="n">
+        <v>15277752047</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
@@ -2331,6 +2555,14 @@
           <t>2024-06-04</t>
         </is>
       </c>
+      <c r="L38" t="n">
+        <v>435.37</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2338,10 +2570,8 @@
           <t>吴磊</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>13669993867</t>
-        </is>
+      <c r="B39" t="n">
+        <v>13669993867</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2378,6 +2608,14 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="L39" t="n">
+        <v>728.1900000000001</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2385,10 +2623,8 @@
           <t>沈军丽</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>15128120679</t>
-        </is>
+      <c r="B40" t="n">
+        <v>15128120679</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2433,6 +2669,14 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="L40" t="n">
+        <v>455.42</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2440,10 +2684,8 @@
           <t>蒋娟</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>15124210249</t>
-        </is>
+      <c r="B41" t="n">
+        <v>15124210249</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2484,6 +2726,14 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="L41" t="n">
+        <v>773.0599999999999</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2491,10 +2741,8 @@
           <t>姜涛</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>13865940139</t>
-        </is>
+      <c r="B42" t="n">
+        <v>13865940139</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2535,6 +2783,14 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="L42" t="n">
+        <v>614.54</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2542,10 +2798,8 @@
           <t>华平娜</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>18656551256</t>
-        </is>
+      <c r="B43" t="n">
+        <v>18656551256</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2586,6 +2840,14 @@
           <t>2024-02-29</t>
         </is>
       </c>
+      <c r="L43" t="n">
+        <v>748.01</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2593,10 +2855,8 @@
           <t>曹超伟</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>18987603859</t>
-        </is>
+      <c r="B44" t="n">
+        <v>18987603859</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2637,6 +2897,14 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="L44" t="n">
+        <v>649.71</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2644,10 +2912,8 @@
           <t>王伟霞</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>13632480861</t>
-        </is>
+      <c r="B45" t="n">
+        <v>13632480861</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
@@ -2688,6 +2954,14 @@
           <t>2024-05-19</t>
         </is>
       </c>
+      <c r="L45" t="n">
+        <v>581.63</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2695,10 +2969,8 @@
           <t>严明磊</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>18682639821</t>
-        </is>
+      <c r="B46" t="n">
+        <v>18682639821</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
@@ -2739,6 +3011,14 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="L46" t="n">
+        <v>189.42</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2746,10 +3026,8 @@
           <t>姜静</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>18655886753</t>
-        </is>
+      <c r="B47" t="n">
+        <v>18655886753</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2794,6 +3072,14 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="L47" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2801,10 +3087,8 @@
           <t>孔杰华</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>13727028951</t>
-        </is>
+      <c r="B48" t="n">
+        <v>13727028951</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2841,6 +3125,14 @@
           <t>2024-03-20</t>
         </is>
       </c>
+      <c r="L48" t="n">
+        <v>699.6900000000001</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2848,10 +3140,8 @@
           <t>周明军</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>15896158657</t>
-        </is>
+      <c r="B49" t="n">
+        <v>15896158657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2896,6 +3186,14 @@
           <t>2024-11-20</t>
         </is>
       </c>
+      <c r="L49" t="n">
+        <v>82.09</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2903,10 +3201,8 @@
           <t>郑涛</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>15200504556</t>
-        </is>
+      <c r="B50" t="n">
+        <v>15200504556</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
@@ -2943,6 +3239,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="L50" t="n">
+        <v>674.52</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2950,10 +3254,8 @@
           <t>杨明静</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>15174740748</t>
-        </is>
+      <c r="B51" t="n">
+        <v>15174740748</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
@@ -2994,6 +3296,14 @@
           <t>2024-04-11</t>
         </is>
       </c>
+      <c r="L51" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3001,10 +3311,8 @@
           <t>孔明</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>15995944064</t>
-        </is>
+      <c r="B52" t="n">
+        <v>15995944064</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
@@ -3041,6 +3349,14 @@
           <t>2024-04-22</t>
         </is>
       </c>
+      <c r="L52" t="n">
+        <v>452.38</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3048,10 +3364,8 @@
           <t>蒋霞</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>13621047095</t>
-        </is>
+      <c r="B53" t="n">
+        <v>13621047095</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3096,6 +3410,14 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="L53" t="n">
+        <v>522.73</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3103,10 +3425,8 @@
           <t>秦丽</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>13774517123</t>
-        </is>
+      <c r="B54" t="n">
+        <v>13774517123</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3147,6 +3467,14 @@
           <t>2024-03-04</t>
         </is>
       </c>
+      <c r="L54" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3154,10 +3482,8 @@
           <t>魏艳刚</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>15296513709</t>
-        </is>
+      <c r="B55" t="n">
+        <v>15296513709</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3198,6 +3524,14 @@
           <t>2024-01-24</t>
         </is>
       </c>
+      <c r="L55" t="n">
+        <v>153.19</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3205,10 +3539,8 @@
           <t>孙洋敏</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>13938267586</t>
-        </is>
+      <c r="B56" t="n">
+        <v>13938267586</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3253,6 +3585,14 @@
           <t>2024-04-21</t>
         </is>
       </c>
+      <c r="L56" t="n">
+        <v>397.27</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3260,10 +3600,8 @@
           <t>金涛艳</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>13958506431</t>
-        </is>
+      <c r="B57" t="n">
+        <v>13958506431</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3308,6 +3646,14 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="L57" t="n">
+        <v>173.43</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3315,10 +3661,8 @@
           <t>沈娜秀</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>15193352904</t>
-        </is>
+      <c r="B58" t="n">
+        <v>15193352904</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3359,6 +3703,14 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="L58" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3366,10 +3718,8 @@
           <t>何伟</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>13826811775</t>
-        </is>
+      <c r="B59" t="n">
+        <v>13826811775</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3410,6 +3760,14 @@
           <t>2024-01-16</t>
         </is>
       </c>
+      <c r="L59" t="n">
+        <v>641.63</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3417,10 +3775,8 @@
           <t>李明娟</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>18917711592</t>
-        </is>
+      <c r="B60" t="n">
+        <v>18917711592</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
@@ -3461,6 +3817,14 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="L60" t="n">
+        <v>246.29</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3468,10 +3832,8 @@
           <t>华敏敏</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>13783673657</t>
-        </is>
+      <c r="B61" t="n">
+        <v>13783673657</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3512,6 +3874,14 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="L61" t="n">
+        <v>445.86</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3519,10 +3889,8 @@
           <t>周娜娜</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>15915280988</t>
-        </is>
+      <c r="B62" t="n">
+        <v>15915280988</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3567,6 +3935,14 @@
           <t>2024-10-22</t>
         </is>
       </c>
+      <c r="L62" t="n">
+        <v>695.03</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3574,10 +3950,8 @@
           <t>沈静磊</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>13715851493</t>
-        </is>
+      <c r="B63" t="n">
+        <v>13715851493</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3614,6 +3988,14 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="L63" t="n">
+        <v>677.63</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3621,10 +4003,8 @@
           <t>许勇</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>15029612018</t>
-        </is>
+      <c r="B64" t="n">
+        <v>15029612018</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
@@ -3661,6 +4041,14 @@
           <t>2024-10-17</t>
         </is>
       </c>
+      <c r="L64" t="n">
+        <v>289.99</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3668,10 +4056,8 @@
           <t>吴芳</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>13690147679</t>
-        </is>
+      <c r="B65" t="n">
+        <v>13690147679</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3708,6 +4094,14 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="L65" t="n">
+        <v>384.96</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3715,10 +4109,8 @@
           <t>姜超芳</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>15169003432</t>
-        </is>
+      <c r="B66" t="n">
+        <v>15169003432</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3759,6 +4151,14 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="L66" t="n">
+        <v>460.97</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3766,10 +4166,8 @@
           <t>韩超刚</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>13651606071</t>
-        </is>
+      <c r="B67" t="n">
+        <v>13651606071</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3810,6 +4208,14 @@
           <t>2024-06-15</t>
         </is>
       </c>
+      <c r="L67" t="n">
+        <v>575.02</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3817,10 +4223,8 @@
           <t>褚华涛</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>13751613696</t>
-        </is>
+      <c r="B68" t="n">
+        <v>13751613696</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3861,6 +4265,14 @@
           <t>2024-02-28</t>
         </is>
       </c>
+      <c r="L68" t="n">
+        <v>375.39</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3868,10 +4280,8 @@
           <t>蒋文</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>13523124329</t>
-        </is>
+      <c r="B69" t="n">
+        <v>13523124329</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -3904,6 +4314,14 @@
           <t>2024-10-23</t>
         </is>
       </c>
+      <c r="L69" t="n">
+        <v>764.62</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3911,10 +4329,8 @@
           <t>金刚兰</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>18995527177</t>
-        </is>
+      <c r="B70" t="n">
+        <v>18995527177</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3951,6 +4367,14 @@
           <t>2024-01-20</t>
         </is>
       </c>
+      <c r="L70" t="n">
+        <v>598.62</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3958,10 +4382,8 @@
           <t>李艳娜</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>18919986798</t>
-        </is>
+      <c r="B71" t="n">
+        <v>18919986798</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4006,6 +4428,14 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="L71" t="n">
+        <v>507.02</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4013,10 +4443,8 @@
           <t>陈芳</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>13651820377</t>
-        </is>
+      <c r="B72" t="n">
+        <v>13651820377</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4061,6 +4489,14 @@
           <t>2024-01-27</t>
         </is>
       </c>
+      <c r="L72" t="n">
+        <v>122.81</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4068,10 +4504,8 @@
           <t>吕娜</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>18764492519</t>
-        </is>
+      <c r="B73" t="n">
+        <v>18764492519</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4108,6 +4542,14 @@
           <t>2024-11-25</t>
         </is>
       </c>
+      <c r="L73" t="n">
+        <v>541.38</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4115,10 +4557,8 @@
           <t>吕静英</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>18981685054</t>
-        </is>
+      <c r="B74" t="n">
+        <v>18981685054</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
@@ -4159,6 +4599,14 @@
           <t>2024-02-09</t>
         </is>
       </c>
+      <c r="L74" t="n">
+        <v>222.27</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4166,10 +4614,8 @@
           <t>尤华</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>13688059296</t>
-        </is>
+      <c r="B75" t="n">
+        <v>13688059296</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
@@ -4210,6 +4656,14 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="L75" t="n">
+        <v>206.55</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4217,10 +4671,8 @@
           <t>金霞</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>13573834735</t>
-        </is>
+      <c r="B76" t="n">
+        <v>13573834735</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4265,6 +4717,14 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="L76" t="n">
+        <v>519.61</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4272,10 +4732,8 @@
           <t>冯军</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>18658181412</t>
-        </is>
+      <c r="B77" t="n">
+        <v>18658181412</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -4312,6 +4770,14 @@
           <t>2024-07-31</t>
         </is>
       </c>
+      <c r="L77" t="n">
+        <v>611.8</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4319,10 +4785,8 @@
           <t>李杰磊</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>15915305152</t>
-        </is>
+      <c r="B78" t="n">
+        <v>15915305152</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
@@ -4363,6 +4827,14 @@
           <t>2024-02-10</t>
         </is>
       </c>
+      <c r="L78" t="n">
+        <v>722.5700000000001</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4370,10 +4842,8 @@
           <t>钱军</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>15089861434</t>
-        </is>
+      <c r="B79" t="n">
+        <v>15089861434</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
@@ -4414,6 +4884,14 @@
           <t>2024-11-01</t>
         </is>
       </c>
+      <c r="L79" t="n">
+        <v>418.66</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4421,10 +4899,8 @@
           <t>钱平磊</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>13524609539</t>
-        </is>
+      <c r="B80" t="n">
+        <v>13524609539</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4469,6 +4945,14 @@
           <t>2024-01-23</t>
         </is>
       </c>
+      <c r="L80" t="n">
+        <v>208.27</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4476,10 +4960,8 @@
           <t>孔艳</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>13851531952</t>
-        </is>
+      <c r="B81" t="n">
+        <v>13851531952</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
@@ -4516,6 +4998,14 @@
           <t>2024-03-10</t>
         </is>
       </c>
+      <c r="L81" t="n">
+        <v>440.76</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4523,10 +5013,8 @@
           <t>周桂涛</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>13843030548</t>
-        </is>
+      <c r="B82" t="n">
+        <v>13843030548</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4567,6 +5055,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="L82" t="n">
+        <v>487.77</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4574,10 +5070,8 @@
           <t>吕军</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>15866765277</t>
-        </is>
+      <c r="B83" t="n">
+        <v>15866765277</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4622,6 +5116,14 @@
           <t>2024-06-13</t>
         </is>
       </c>
+      <c r="L83" t="n">
+        <v>678.3200000000001</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4629,10 +5131,8 @@
           <t>郑娜</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>15247962757</t>
-        </is>
+      <c r="B84" t="n">
+        <v>15247962757</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
@@ -4669,6 +5169,14 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="L84" t="n">
+        <v>311.82</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4676,10 +5184,8 @@
           <t>张超刚</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>15002970213</t>
-        </is>
+      <c r="B85" t="n">
+        <v>15002970213</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4724,6 +5230,14 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="L85" t="n">
+        <v>626.22</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4731,10 +5245,8 @@
           <t>冯超</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>15843102786</t>
-        </is>
+      <c r="B86" t="n">
+        <v>15843102786</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4775,6 +5287,14 @@
           <t>2024-03-10</t>
         </is>
       </c>
+      <c r="L86" t="n">
+        <v>499.92</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4782,10 +5302,8 @@
           <t>周涛</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>13571551884</t>
-        </is>
+      <c r="B87" t="n">
+        <v>13571551884</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4826,6 +5344,14 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="L87" t="n">
+        <v>246.25</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4833,10 +5359,8 @@
           <t>姜伟</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>18857829114</t>
-        </is>
+      <c r="B88" t="n">
+        <v>18857829114</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4877,6 +5401,14 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="L88" t="n">
+        <v>166.86</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4884,10 +5416,8 @@
           <t>周涛</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>18752892268</t>
-        </is>
+      <c r="B89" t="n">
+        <v>18752892268</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4928,6 +5458,14 @@
           <t>2024-04-25</t>
         </is>
       </c>
+      <c r="L89" t="n">
+        <v>322.37</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4935,10 +5473,8 @@
           <t>施超娜</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>15238424981</t>
-        </is>
+      <c r="B90" t="n">
+        <v>15238424981</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4975,6 +5511,14 @@
           <t>2024-02-11</t>
         </is>
       </c>
+      <c r="L90" t="n">
+        <v>349.89</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4982,10 +5526,8 @@
           <t>孙平军</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>18939690784</t>
-        </is>
+      <c r="B91" t="n">
+        <v>18939690784</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5026,6 +5568,14 @@
           <t>2024-07-31</t>
         </is>
       </c>
+      <c r="L91" t="n">
+        <v>590.85</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5033,10 +5583,8 @@
           <t>陶涛</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>18825556258</t>
-        </is>
+      <c r="B92" t="n">
+        <v>18825556258</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -5077,6 +5625,14 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="L92" t="n">
+        <v>677.5700000000001</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5084,10 +5640,8 @@
           <t>孔霞</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>13725953278</t>
-        </is>
+      <c r="B93" t="n">
+        <v>13725953278</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5132,6 +5686,14 @@
           <t>2024-06-29</t>
         </is>
       </c>
+      <c r="L93" t="n">
+        <v>204.41</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5139,10 +5701,8 @@
           <t>李芳</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>18874801624</t>
-        </is>
+      <c r="B94" t="n">
+        <v>18874801624</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -5183,6 +5743,14 @@
           <t>2024-05-27</t>
         </is>
       </c>
+      <c r="L94" t="n">
+        <v>285.56</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5190,10 +5758,8 @@
           <t>周杰文</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>18749912165</t>
-        </is>
+      <c r="B95" t="n">
+        <v>18749912165</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5234,6 +5800,14 @@
           <t>2024-01-24</t>
         </is>
       </c>
+      <c r="L95" t="n">
+        <v>434.1</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5241,10 +5815,8 @@
           <t>孙静华</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>18687298259</t>
-        </is>
+      <c r="B96" t="n">
+        <v>18687298259</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5285,6 +5857,14 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="L96" t="n">
+        <v>639.37</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5292,10 +5872,8 @@
           <t>陶伟</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>18916940974</t>
-        </is>
+      <c r="B97" t="n">
+        <v>18916940974</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5336,6 +5914,14 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="L97" t="n">
+        <v>381.47</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5343,10 +5929,8 @@
           <t>孙兰敏</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>15107562636</t>
-        </is>
+      <c r="B98" t="n">
+        <v>15107562636</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5391,6 +5975,14 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="L98" t="n">
+        <v>483.07</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5398,10 +5990,8 @@
           <t>孔勇涛</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>18758549733</t>
-        </is>
+      <c r="B99" t="n">
+        <v>18758549733</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
@@ -5442,6 +6032,14 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="L99" t="n">
+        <v>673.91</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5449,10 +6047,8 @@
           <t>何明</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>13644198665</t>
-        </is>
+      <c r="B100" t="n">
+        <v>13644198665</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5493,6 +6089,14 @@
           <t>2024-05-11</t>
         </is>
       </c>
+      <c r="L100" t="n">
+        <v>433.27</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5500,10 +6104,8 @@
           <t>陶强</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>18748421993</t>
-        </is>
+      <c r="B101" t="n">
+        <v>18748421993</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
@@ -5536,6 +6138,14 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="L101" t="n">
+        <v>722.1900000000001</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5543,10 +6153,8 @@
           <t>陶敏静</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>13882677345</t>
-        </is>
+      <c r="B102" t="n">
+        <v>13882677345</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
@@ -5587,6 +6195,14 @@
           <t>2024-03-31</t>
         </is>
       </c>
+      <c r="L102" t="n">
+        <v>292.54</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5594,10 +6210,8 @@
           <t>孙杰丽</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>13540049915</t>
-        </is>
+      <c r="B103" t="n">
+        <v>13540049915</v>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
@@ -5634,6 +6248,14 @@
           <t>2024-02-27</t>
         </is>
       </c>
+      <c r="L103" t="n">
+        <v>458.37</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5641,10 +6263,8 @@
           <t>吕丽平</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>15220549329</t>
-        </is>
+      <c r="B104" t="n">
+        <v>15220549329</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5685,6 +6305,14 @@
           <t>2024-09-01</t>
         </is>
       </c>
+      <c r="L104" t="n">
+        <v>670.77</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5692,10 +6320,8 @@
           <t>何磊</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>15937454990</t>
-        </is>
+      <c r="B105" t="n">
+        <v>15937454990</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
@@ -5732,6 +6358,14 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="L105" t="n">
+        <v>443.05</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5739,10 +6373,8 @@
           <t>许桂</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>15259332727</t>
-        </is>
+      <c r="B106" t="n">
+        <v>15259332727</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5787,6 +6419,14 @@
           <t>2024-02-11</t>
         </is>
       </c>
+      <c r="L106" t="n">
+        <v>170.65</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5794,10 +6434,8 @@
           <t>金超娜</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>18810883982</t>
-        </is>
+      <c r="B107" t="n">
+        <v>18810883982</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
@@ -5830,6 +6468,14 @@
           <t>2024-08-16</t>
         </is>
       </c>
+      <c r="L107" t="n">
+        <v>746.91</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5837,10 +6483,8 @@
           <t>李涛</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>15979087406</t>
-        </is>
+      <c r="B108" t="n">
+        <v>15979087406</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
@@ -5881,6 +6525,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="L108" t="n">
+        <v>778.67</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5888,10 +6540,8 @@
           <t>李娜明</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>13846226567</t>
-        </is>
+      <c r="B109" t="n">
+        <v>13846226567</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5932,6 +6582,14 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="L109" t="n">
+        <v>485.61</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5939,10 +6597,8 @@
           <t>冯英伟</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>13604786863</t>
-        </is>
+      <c r="B110" t="n">
+        <v>13604786863</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
@@ -5979,6 +6635,14 @@
           <t>2024-08-02</t>
         </is>
       </c>
+      <c r="L110" t="n">
+        <v>326.74</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5986,10 +6650,8 @@
           <t>钱磊</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>13990790306</t>
-        </is>
+      <c r="B111" t="n">
+        <v>13990790306</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -6034,6 +6696,14 @@
           <t>2024-12-10</t>
         </is>
       </c>
+      <c r="L111" t="n">
+        <v>396.12</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6041,10 +6711,8 @@
           <t>何磊</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>15083644089</t>
-        </is>
+      <c r="B112" t="n">
+        <v>15083644089</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -6085,6 +6753,14 @@
           <t>2024-06-12</t>
         </is>
       </c>
+      <c r="L112" t="n">
+        <v>450.49</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6092,10 +6768,8 @@
           <t>严娟</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>15928733427</t>
-        </is>
+      <c r="B113" t="n">
+        <v>15928733427</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -6140,6 +6814,14 @@
           <t>2024-11-27</t>
         </is>
       </c>
+      <c r="L113" t="n">
+        <v>642.8099999999999</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6147,10 +6829,8 @@
           <t>吴涛娜</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>18730469901</t>
-        </is>
+      <c r="B114" t="n">
+        <v>18730469901</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -6183,6 +6863,14 @@
           <t>2024-04-18</t>
         </is>
       </c>
+      <c r="L114" t="n">
+        <v>691.0599999999999</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6190,10 +6878,8 @@
           <t>蒋英</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>13673936385</t>
-        </is>
+      <c r="B115" t="n">
+        <v>13673936385</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -6230,6 +6916,14 @@
           <t>2024-08-28</t>
         </is>
       </c>
+      <c r="L115" t="n">
+        <v>120.41</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6237,10 +6931,8 @@
           <t>何强</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>15909320489</t>
-        </is>
+      <c r="B116" t="n">
+        <v>15909320489</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -6281,6 +6973,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="L116" t="n">
+        <v>467.14</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6288,10 +6988,8 @@
           <t>吕军明</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>13577252287</t>
-        </is>
+      <c r="B117" t="n">
+        <v>13577252287</v>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
@@ -6328,6 +7026,14 @@
           <t>2024-11-18</t>
         </is>
       </c>
+      <c r="L117" t="n">
+        <v>114.48</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6335,10 +7041,8 @@
           <t>韩娜伟</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>15187509977</t>
-        </is>
+      <c r="B118" t="n">
+        <v>15187509977</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -6371,6 +7075,14 @@
           <t>2024-01-09</t>
         </is>
       </c>
+      <c r="L118" t="n">
+        <v>681.0599999999999</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6378,10 +7090,8 @@
           <t>华华丽</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>13918233984</t>
-        </is>
+      <c r="B119" t="n">
+        <v>13918233984</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6422,6 +7132,14 @@
           <t>2024-12-22</t>
         </is>
       </c>
+      <c r="L119" t="n">
+        <v>310.69</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6429,10 +7147,8 @@
           <t>韩洋娜</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>18901666870</t>
-        </is>
+      <c r="B120" t="n">
+        <v>18901666870</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6477,6 +7193,14 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="L120" t="n">
+        <v>406.23</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6484,10 +7208,8 @@
           <t>陶军</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>13948902503</t>
-        </is>
+      <c r="B121" t="n">
+        <v>13948902503</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6528,6 +7250,14 @@
           <t>2024-12-12</t>
         </is>
       </c>
+      <c r="L121" t="n">
+        <v>522.22</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6535,10 +7265,8 @@
           <t>吕杰静</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>13618501631</t>
-        </is>
+      <c r="B122" t="n">
+        <v>13618501631</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6579,6 +7307,14 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="L122" t="n">
+        <v>419.02</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6586,10 +7322,8 @@
           <t>韩艳杰</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>15929619431</t>
-        </is>
+      <c r="B123" t="n">
+        <v>15929619431</v>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
@@ -6630,6 +7364,14 @@
           <t>2024-02-16</t>
         </is>
       </c>
+      <c r="L123" t="n">
+        <v>124.04</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6637,10 +7379,8 @@
           <t>赵洋</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>13641212678</t>
-        </is>
+      <c r="B124" t="n">
+        <v>13641212678</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6681,6 +7421,14 @@
           <t>2024-01-07</t>
         </is>
       </c>
+      <c r="L124" t="n">
+        <v>94.04000000000001</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6688,10 +7436,8 @@
           <t>尤娟</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>13983982622</t>
-        </is>
+      <c r="B125" t="n">
+        <v>13983982622</v>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
@@ -6728,6 +7474,14 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="L125" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6735,10 +7489,8 @@
           <t>陶华</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>15237993712</t>
-        </is>
+      <c r="B126" t="n">
+        <v>15237993712</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6779,6 +7531,14 @@
           <t>2024-10-31</t>
         </is>
       </c>
+      <c r="L126" t="n">
+        <v>172.24</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6786,10 +7546,8 @@
           <t>冯洋</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>13537526547</t>
-        </is>
+      <c r="B127" t="n">
+        <v>13537526547</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6830,6 +7588,14 @@
           <t>2024-04-12</t>
         </is>
       </c>
+      <c r="L127" t="n">
+        <v>700.73</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6837,10 +7603,8 @@
           <t>卫刚伟</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>13573741672</t>
-        </is>
+      <c r="B128" t="n">
+        <v>13573741672</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6881,6 +7645,14 @@
           <t>2024-10-25</t>
         </is>
       </c>
+      <c r="L128" t="n">
+        <v>287.55</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6888,10 +7660,8 @@
           <t>曹秀桂</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>15980589113</t>
-        </is>
+      <c r="B129" t="n">
+        <v>15980589113</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6932,6 +7702,14 @@
           <t>2024-02-20</t>
         </is>
       </c>
+      <c r="L129" t="n">
+        <v>791.71</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6939,10 +7717,8 @@
           <t>朱磊超</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>18799375679</t>
-        </is>
+      <c r="B130" t="n">
+        <v>18799375679</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6983,6 +7759,14 @@
           <t>2024-03-13</t>
         </is>
       </c>
+      <c r="L130" t="n">
+        <v>221.42</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6990,10 +7774,8 @@
           <t>施洋</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>13638757177</t>
-        </is>
+      <c r="B131" t="n">
+        <v>13638757177</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -7030,6 +7812,14 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="L131" t="n">
+        <v>483.28</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7037,10 +7827,8 @@
           <t>卫秀</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>18767362266</t>
-        </is>
+      <c r="B132" t="n">
+        <v>18767362266</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
@@ -7073,6 +7861,14 @@
           <t>2024-04-19</t>
         </is>
       </c>
+      <c r="L132" t="n">
+        <v>522.76</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7080,10 +7876,8 @@
           <t>沈军华</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>13619182553</t>
-        </is>
+      <c r="B133" t="n">
+        <v>13619182553</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -7128,6 +7922,14 @@
           <t>2024-06-27</t>
         </is>
       </c>
+      <c r="L133" t="n">
+        <v>372.92</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7135,10 +7937,8 @@
           <t>施涛刚</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>13549912513</t>
-        </is>
+      <c r="B134" t="n">
+        <v>13549912513</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -7179,6 +7979,14 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="L134" t="n">
+        <v>444.03</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7186,10 +7994,8 @@
           <t>卫秀</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>15222579050</t>
-        </is>
+      <c r="B135" t="n">
+        <v>15222579050</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -7234,6 +8040,14 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="L135" t="n">
+        <v>534.6</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7241,10 +8055,8 @@
           <t>姜丽</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>13834043842</t>
-        </is>
+      <c r="B136" t="n">
+        <v>13834043842</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -7289,6 +8101,14 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="L136" t="n">
+        <v>696.9400000000001</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7296,10 +8116,8 @@
           <t>孙文秀</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>15161340745</t>
-        </is>
+      <c r="B137" t="n">
+        <v>15161340745</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -7340,6 +8158,14 @@
           <t>2024-03-12</t>
         </is>
       </c>
+      <c r="L137" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7347,10 +8173,8 @@
           <t>沈强兰</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>15884982544</t>
-        </is>
+      <c r="B138" t="n">
+        <v>15884982544</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -7387,6 +8211,14 @@
           <t>2024-03-05</t>
         </is>
       </c>
+      <c r="L138" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7394,10 +8226,8 @@
           <t>冯磊</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>15836729466</t>
-        </is>
+      <c r="B139" t="n">
+        <v>15836729466</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -7442,6 +8272,14 @@
           <t>2024-10-24</t>
         </is>
       </c>
+      <c r="L139" t="n">
+        <v>551.42</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7449,10 +8287,8 @@
           <t>赵文娜</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>13575186363</t>
-        </is>
+      <c r="B140" t="n">
+        <v>13575186363</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7497,6 +8333,14 @@
           <t>2024-01-24</t>
         </is>
       </c>
+      <c r="L140" t="n">
+        <v>224.62</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7504,10 +8348,8 @@
           <t>郑平涛</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>13812770632</t>
-        </is>
+      <c r="B141" t="n">
+        <v>13812770632</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7552,6 +8394,14 @@
           <t>2024-03-25</t>
         </is>
       </c>
+      <c r="L141" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7559,10 +8409,8 @@
           <t>李杰英</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>13536110371</t>
-        </is>
+      <c r="B142" t="n">
+        <v>13536110371</v>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
@@ -7603,6 +8451,14 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="L142" t="n">
+        <v>583.77</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7610,10 +8466,8 @@
           <t>冯明</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>15911155426</t>
-        </is>
+      <c r="B143" t="n">
+        <v>15911155426</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7654,6 +8508,14 @@
           <t>2024-04-19</t>
         </is>
       </c>
+      <c r="L143" t="n">
+        <v>175.93</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7661,10 +8523,8 @@
           <t>陈娟涛</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>13731121965</t>
-        </is>
+      <c r="B144" t="n">
+        <v>13731121965</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7705,6 +8565,14 @@
           <t>2024-11-03</t>
         </is>
       </c>
+      <c r="L144" t="n">
+        <v>338.41</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7712,10 +8580,8 @@
           <t>尤文伟</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>13743898364</t>
-        </is>
+      <c r="B145" t="n">
+        <v>13743898364</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7756,6 +8622,14 @@
           <t>2024-02-06</t>
         </is>
       </c>
+      <c r="L145" t="n">
+        <v>155.87</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7763,10 +8637,8 @@
           <t>赵艳静</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>15996582710</t>
-        </is>
+      <c r="B146" t="n">
+        <v>15996582710</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7811,6 +8683,14 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="L146" t="n">
+        <v>525.76</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7818,10 +8698,8 @@
           <t>严娟娜</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>18988924141</t>
-        </is>
+      <c r="B147" t="n">
+        <v>18988924141</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7862,6 +8740,14 @@
           <t>2024-05-02</t>
         </is>
       </c>
+      <c r="L147" t="n">
+        <v>614.88</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7869,10 +8755,8 @@
           <t>李磊</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>15917990421</t>
-        </is>
+      <c r="B148" t="n">
+        <v>15917990421</v>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
@@ -7909,6 +8793,14 @@
           <t>2024-03-05</t>
         </is>
       </c>
+      <c r="L148" t="n">
+        <v>502.62</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7916,10 +8808,8 @@
           <t>秦英文</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>13856481491</t>
-        </is>
+      <c r="B149" t="n">
+        <v>13856481491</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7964,6 +8854,14 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="L149" t="n">
+        <v>339.74</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7971,10 +8869,8 @@
           <t>王磊伟</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>13803075622</t>
-        </is>
+      <c r="B150" t="n">
+        <v>13803075622</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -8011,6 +8907,14 @@
           <t>2024-05-18</t>
         </is>
       </c>
+      <c r="L150" t="n">
+        <v>755.28</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8018,10 +8922,8 @@
           <t>周兰</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>18702380617</t>
-        </is>
+      <c r="B151" t="n">
+        <v>18702380617</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -8062,6 +8964,14 @@
           <t>2024-05-29</t>
         </is>
       </c>
+      <c r="L151" t="n">
+        <v>786.03</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8069,10 +8979,8 @@
           <t>许英涛</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>15897383206</t>
-        </is>
+      <c r="B152" t="n">
+        <v>15897383206</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
@@ -8109,6 +9017,14 @@
           <t>2024-07-11</t>
         </is>
       </c>
+      <c r="L152" t="n">
+        <v>194.62</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8116,10 +9032,8 @@
           <t>许敏</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>15167024103</t>
-        </is>
+      <c r="B153" t="n">
+        <v>15167024103</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -8156,6 +9070,14 @@
           <t>2024-11-22</t>
         </is>
       </c>
+      <c r="L153" t="n">
+        <v>781.78</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8163,10 +9085,8 @@
           <t>曹娜芳</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>15923445655</t>
-        </is>
+      <c r="B154" t="n">
+        <v>15923445655</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -8211,6 +9131,14 @@
           <t>2024-08-26</t>
         </is>
       </c>
+      <c r="L154" t="n">
+        <v>789.15</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8218,10 +9146,8 @@
           <t>何娟</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>15837474112</t>
-        </is>
+      <c r="B155" t="n">
+        <v>15837474112</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -8258,6 +9184,14 @@
           <t>2024-05-07</t>
         </is>
       </c>
+      <c r="L155" t="n">
+        <v>679.99</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8265,10 +9199,8 @@
           <t>施杰刚</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>15242067883</t>
-        </is>
+      <c r="B156" t="n">
+        <v>15242067883</v>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
@@ -8305,6 +9237,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="L156" t="n">
+        <v>148.85</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8312,10 +9252,8 @@
           <t>张刚平</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>13999410137</t>
-        </is>
+      <c r="B157" t="n">
+        <v>13999410137</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -8356,6 +9294,14 @@
           <t>2024-08-09</t>
         </is>
       </c>
+      <c r="L157" t="n">
+        <v>710.6</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8363,10 +9309,8 @@
           <t>曹明</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>18962532447</t>
-        </is>
+      <c r="B158" t="n">
+        <v>18962532447</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -8407,6 +9351,14 @@
           <t>2024-05-23</t>
         </is>
       </c>
+      <c r="L158" t="n">
+        <v>742.59</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8414,10 +9366,8 @@
           <t>孔静</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>18983806578</t>
-        </is>
+      <c r="B159" t="n">
+        <v>18983806578</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -8454,6 +9404,14 @@
           <t>2024-11-01</t>
         </is>
       </c>
+      <c r="L159" t="n">
+        <v>731.89</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8461,10 +9419,8 @@
           <t>韩伟文</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>15207859321</t>
-        </is>
+      <c r="B160" t="n">
+        <v>15207859321</v>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
@@ -8505,6 +9461,14 @@
           <t>2024-03-31</t>
         </is>
       </c>
+      <c r="L160" t="n">
+        <v>114.13</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8512,10 +9476,8 @@
           <t>杨兰</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>13559059929</t>
-        </is>
+      <c r="B161" t="n">
+        <v>13559059929</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -8556,6 +9518,14 @@
           <t>2024-04-29</t>
         </is>
       </c>
+      <c r="L161" t="n">
+        <v>738.52</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8563,10 +9533,8 @@
           <t>韩伟伟</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>15893252500</t>
-        </is>
+      <c r="B162" t="n">
+        <v>15893252500</v>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
@@ -8603,6 +9571,14 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="L162" t="n">
+        <v>706.34</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8610,10 +9586,8 @@
           <t>曹兰</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>15252267528</t>
-        </is>
+      <c r="B163" t="n">
+        <v>15252267528</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8658,6 +9632,14 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="L163" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8665,10 +9647,8 @@
           <t>冯丽桂</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>18869029593</t>
-        </is>
+      <c r="B164" t="n">
+        <v>18869029593</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8709,6 +9689,14 @@
           <t>2024-03-26</t>
         </is>
       </c>
+      <c r="L164" t="n">
+        <v>777.4299999999999</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8716,10 +9704,8 @@
           <t>吴桂英</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>15870433154</t>
-        </is>
+      <c r="B165" t="n">
+        <v>15870433154</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8760,6 +9746,14 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="L165" t="n">
+        <v>633.14</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8767,10 +9761,8 @@
           <t>施秀</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>13779327104</t>
-        </is>
+      <c r="B166" t="n">
+        <v>13779327104</v>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
@@ -8807,6 +9799,14 @@
           <t>2024-02-08</t>
         </is>
       </c>
+      <c r="L166" t="n">
+        <v>218.58</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8814,10 +9814,8 @@
           <t>吴勇霞</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>18606296201</t>
-        </is>
+      <c r="B167" t="n">
+        <v>18606296201</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -8858,6 +9856,14 @@
           <t>2024-02-19</t>
         </is>
       </c>
+      <c r="L167" t="n">
+        <v>675.67</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8865,10 +9871,8 @@
           <t>李杰明</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>15005061497</t>
-        </is>
+      <c r="B168" t="n">
+        <v>15005061497</v>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
@@ -8905,6 +9909,14 @@
           <t>2024-06-06</t>
         </is>
       </c>
+      <c r="L168" t="n">
+        <v>616.33</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8912,10 +9924,8 @@
           <t>曹明</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>18941862565</t>
-        </is>
+      <c r="B169" t="n">
+        <v>18941862565</v>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
@@ -8952,6 +9962,14 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="L169" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8959,10 +9977,8 @@
           <t>李静刚</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>13915869380</t>
-        </is>
+      <c r="B170" t="n">
+        <v>13915869380</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -9007,6 +10023,14 @@
           <t>2024-07-21</t>
         </is>
       </c>
+      <c r="L170" t="n">
+        <v>732.05</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9014,10 +10038,8 @@
           <t>孙超超</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>13699217223</t>
-        </is>
+      <c r="B171" t="n">
+        <v>13699217223</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -9062,6 +10084,14 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="L171" t="n">
+        <v>572.03</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9069,10 +10099,8 @@
           <t>何英娜</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>13968685487</t>
-        </is>
+      <c r="B172" t="n">
+        <v>13968685487</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -9113,6 +10141,14 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="L172" t="n">
+        <v>439.11</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9120,10 +10156,8 @@
           <t>郑敏敏</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>13648564679</t>
-        </is>
+      <c r="B173" t="n">
+        <v>13648564679</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -9164,6 +10198,14 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="L173" t="n">
+        <v>410.18</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9171,10 +10213,8 @@
           <t>杨芳军</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>15805444713</t>
-        </is>
+      <c r="B174" t="n">
+        <v>15805444713</v>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
@@ -9211,6 +10251,14 @@
           <t>2024-02-15</t>
         </is>
       </c>
+      <c r="L174" t="n">
+        <v>692.1</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9218,10 +10266,8 @@
           <t>蒋涛</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>13767850821</t>
-        </is>
+      <c r="B175" t="n">
+        <v>13767850821</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -9266,6 +10312,14 @@
           <t>2024-01-30</t>
         </is>
       </c>
+      <c r="L175" t="n">
+        <v>692.99</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9273,10 +10327,8 @@
           <t>杨芳</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>15834578610</t>
-        </is>
+      <c r="B176" t="n">
+        <v>15834578610</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
@@ -9313,6 +10365,14 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="L176" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9320,10 +10380,8 @@
           <t>吴洋</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>13829333346</t>
-        </is>
+      <c r="B177" t="n">
+        <v>13829333346</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -9360,6 +10418,14 @@
           <t>2024-04-24</t>
         </is>
       </c>
+      <c r="L177" t="n">
+        <v>154.58</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9367,10 +10433,8 @@
           <t>朱霞洋</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>13546657437</t>
-        </is>
+      <c r="B178" t="n">
+        <v>13546657437</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -9411,6 +10475,14 @@
           <t>2024-10-31</t>
         </is>
       </c>
+      <c r="L178" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9418,10 +10490,8 @@
           <t>尤洋明</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>13954544432</t>
-        </is>
+      <c r="B179" t="n">
+        <v>13954544432</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -9466,6 +10536,14 @@
           <t>2024-08-02</t>
         </is>
       </c>
+      <c r="L179" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9473,10 +10551,8 @@
           <t>曹杰兰</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>13593538758</t>
-        </is>
+      <c r="B180" t="n">
+        <v>13593538758</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -9513,6 +10589,14 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="L180" t="n">
+        <v>306.86</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9520,10 +10604,8 @@
           <t>卫刚平</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>13935346554</t>
-        </is>
+      <c r="B181" t="n">
+        <v>13935346554</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -9564,6 +10646,14 @@
           <t>2024-03-02</t>
         </is>
       </c>
+      <c r="L181" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9571,10 +10661,8 @@
           <t>孔超</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>13822356972</t>
-        </is>
+      <c r="B182" t="n">
+        <v>13822356972</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -9615,6 +10703,14 @@
           <t>2024-01-03</t>
         </is>
       </c>
+      <c r="L182" t="n">
+        <v>121.91</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9622,10 +10718,8 @@
           <t>金军</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>13629271296</t>
-        </is>
+      <c r="B183" t="n">
+        <v>13629271296</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -9666,6 +10760,14 @@
           <t>2024-01-08</t>
         </is>
       </c>
+      <c r="L183" t="n">
+        <v>660.4400000000001</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9673,10 +10775,8 @@
           <t>何文强</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>13803354216</t>
-        </is>
+      <c r="B184" t="n">
+        <v>13803354216</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -9717,6 +10817,14 @@
           <t>2024-11-01</t>
         </is>
       </c>
+      <c r="L184" t="n">
+        <v>545.27</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9724,10 +10832,8 @@
           <t>吕娟静</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>15875326033</t>
-        </is>
+      <c r="B185" t="n">
+        <v>15875326033</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -9768,6 +10874,14 @@
           <t>2024-01-20</t>
         </is>
       </c>
+      <c r="L185" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9775,10 +10889,8 @@
           <t>孔平</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>18790901001</t>
-        </is>
+      <c r="B186" t="n">
+        <v>18790901001</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -9815,6 +10927,14 @@
           <t>2024-11-18</t>
         </is>
       </c>
+      <c r="L186" t="n">
+        <v>128.99</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9822,10 +10942,8 @@
           <t>赵洋</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>13984992618</t>
-        </is>
+      <c r="B187" t="n">
+        <v>13984992618</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -9866,6 +10984,14 @@
           <t>2024-04-13</t>
         </is>
       </c>
+      <c r="L187" t="n">
+        <v>792.38</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9873,10 +10999,8 @@
           <t>施桂</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>15008737530</t>
-        </is>
+      <c r="B188" t="n">
+        <v>15008737530</v>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
@@ -9917,6 +11041,14 @@
           <t>2024-02-08</t>
         </is>
       </c>
+      <c r="L188" t="n">
+        <v>578.2</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9924,10 +11056,8 @@
           <t>郑军涛</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>15247012045</t>
-        </is>
+      <c r="B189" t="n">
+        <v>15247012045</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -9964,6 +11094,14 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="L189" t="n">
+        <v>138.92</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9971,10 +11109,8 @@
           <t>褚勇</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>18694155216</t>
-        </is>
+      <c r="B190" t="n">
+        <v>18694155216</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -10019,6 +11155,14 @@
           <t>2024-01-31</t>
         </is>
       </c>
+      <c r="L190" t="n">
+        <v>772.62</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10026,10 +11170,8 @@
           <t>褚敏</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>18879729659</t>
-        </is>
+      <c r="B191" t="n">
+        <v>18879729659</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
@@ -10062,6 +11204,14 @@
           <t>2024-01-24</t>
         </is>
       </c>
+      <c r="L191" t="n">
+        <v>246.86</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10069,10 +11219,8 @@
           <t>周军伟</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>13589935889</t>
-        </is>
+      <c r="B192" t="n">
+        <v>13589935889</v>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
@@ -10105,6 +11253,14 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="L192" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10112,10 +11268,8 @@
           <t>李伟丽</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>18777217535</t>
-        </is>
+      <c r="B193" t="n">
+        <v>18777217535</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -10160,6 +11314,14 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="L193" t="n">
+        <v>794.84</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10167,10 +11329,8 @@
           <t>金娜涛</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>15817016608</t>
-        </is>
+      <c r="B194" t="n">
+        <v>15817016608</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -10211,6 +11371,14 @@
           <t>2024-01-28</t>
         </is>
       </c>
+      <c r="L194" t="n">
+        <v>427.31</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10218,10 +11386,8 @@
           <t>韩涛</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>13699757113</t>
-        </is>
+      <c r="B195" t="n">
+        <v>13699757113</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
@@ -10262,6 +11428,14 @@
           <t>2024-03-12</t>
         </is>
       </c>
+      <c r="L195" t="n">
+        <v>684.8200000000001</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10269,10 +11443,8 @@
           <t>严敏</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>15131637351</t>
-        </is>
+      <c r="B196" t="n">
+        <v>15131637351</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -10313,6 +11485,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="L196" t="n">
+        <v>509.64</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10320,10 +11500,8 @@
           <t>李秀兰</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>18682922169</t>
-        </is>
+      <c r="B197" t="n">
+        <v>18682922169</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -10368,6 +11546,14 @@
           <t>2024-08-19</t>
         </is>
       </c>
+      <c r="L197" t="n">
+        <v>480.46</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10375,10 +11561,8 @@
           <t>冯静</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>13584858333</t>
-        </is>
+      <c r="B198" t="n">
+        <v>13584858333</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -10423,6 +11607,14 @@
           <t>2024-06-29</t>
         </is>
       </c>
+      <c r="L198" t="n">
+        <v>780.1</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10430,10 +11622,8 @@
           <t>陶兰刚</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>13568460810</t>
-        </is>
+      <c r="B199" t="n">
+        <v>13568460810</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -10474,6 +11664,14 @@
           <t>2024-03-15</t>
         </is>
       </c>
+      <c r="L199" t="n">
+        <v>120.03</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10481,10 +11679,8 @@
           <t>李桂强</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>13680571983</t>
-        </is>
+      <c r="B200" t="n">
+        <v>13680571983</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -10529,6 +11725,14 @@
           <t>2024-12-16</t>
         </is>
       </c>
+      <c r="L200" t="n">
+        <v>257.12</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10536,10 +11740,8 @@
           <t>何秀</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>13543973598</t>
-        </is>
+      <c r="B201" t="n">
+        <v>13543973598</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -10576,6 +11778,14 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="L201" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10583,10 +11793,8 @@
           <t>王杰</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>15284229405</t>
-        </is>
+      <c r="B202" t="n">
+        <v>15284229405</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -10631,6 +11839,14 @@
           <t>2024-06-11</t>
         </is>
       </c>
+      <c r="L202" t="n">
+        <v>407.02</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10638,10 +11854,8 @@
           <t>韩丽华</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>18726886153</t>
-        </is>
+      <c r="B203" t="n">
+        <v>18726886153</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -10682,6 +11896,14 @@
           <t>2024-01-05</t>
         </is>
       </c>
+      <c r="L203" t="n">
+        <v>623.42</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10689,10 +11911,8 @@
           <t>王刚</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>15199305616</t>
-        </is>
+      <c r="B204" t="n">
+        <v>15199305616</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
@@ -10725,6 +11945,14 @@
           <t>2024-08-16</t>
         </is>
       </c>
+      <c r="L204" t="n">
+        <v>400.83</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10732,10 +11960,8 @@
           <t>姜芳</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>18935811288</t>
-        </is>
+      <c r="B205" t="n">
+        <v>18935811288</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
@@ -10776,6 +12002,14 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="L205" t="n">
+        <v>731.79</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10783,10 +12017,8 @@
           <t>华平娜</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>13520750110</t>
-        </is>
+      <c r="B206" t="n">
+        <v>13520750110</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
@@ -10823,6 +12055,14 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="L206" t="n">
+        <v>238.98</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10830,10 +12070,8 @@
           <t>曹娟</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>15918091901</t>
-        </is>
+      <c r="B207" t="n">
+        <v>15918091901</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -10878,6 +12116,14 @@
           <t>2024-01-16</t>
         </is>
       </c>
+      <c r="L207" t="n">
+        <v>747.66</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10885,10 +12131,8 @@
           <t>陶丽静</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>13568424508</t>
-        </is>
+      <c r="B208" t="n">
+        <v>13568424508</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -10933,6 +12177,14 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="L208" t="n">
+        <v>607.36</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10940,10 +12192,8 @@
           <t>沈娟超</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>15022394312</t>
-        </is>
+      <c r="B209" t="n">
+        <v>15022394312</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -10984,6 +12234,14 @@
           <t>2024-02-04</t>
         </is>
       </c>
+      <c r="L209" t="n">
+        <v>525.53</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10991,10 +12249,8 @@
           <t>朱敏</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>18875523149</t>
-        </is>
+      <c r="B210" t="n">
+        <v>18875523149</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
@@ -11031,6 +12287,14 @@
           <t>2024-03-19</t>
         </is>
       </c>
+      <c r="L210" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11038,10 +12302,8 @@
           <t>张华</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>15920533645</t>
-        </is>
+      <c r="B211" t="n">
+        <v>15920533645</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr"/>
@@ -11078,6 +12340,14 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="L211" t="n">
+        <v>624.89</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11085,10 +12355,8 @@
           <t>郑丽娜</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>13742834110</t>
-        </is>
+      <c r="B212" t="n">
+        <v>13742834110</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -11129,6 +12397,14 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="L212" t="n">
+        <v>354.49</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11136,10 +12412,8 @@
           <t>陈艳</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>13694278816</t>
-        </is>
+      <c r="B213" t="n">
+        <v>13694278816</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -11184,6 +12458,14 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="L213" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11191,10 +12473,8 @@
           <t>陈英艳</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>13837314530</t>
-        </is>
+      <c r="B214" t="n">
+        <v>13837314530</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -11235,6 +12515,14 @@
           <t>2024-06-14</t>
         </is>
       </c>
+      <c r="L214" t="n">
+        <v>215.91</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11242,10 +12530,8 @@
           <t>郑桂平</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>13744989266</t>
-        </is>
+      <c r="B215" t="n">
+        <v>13744989266</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -11286,6 +12572,14 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="L215" t="n">
+        <v>420.39</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11293,10 +12587,8 @@
           <t>陶霞</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>15072318432</t>
-        </is>
+      <c r="B216" t="n">
+        <v>15072318432</v>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
@@ -11337,6 +12629,14 @@
           <t>2024-09-02</t>
         </is>
       </c>
+      <c r="L216" t="n">
+        <v>743.58</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11344,10 +12644,8 @@
           <t>陶强平</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>13760302992</t>
-        </is>
+      <c r="B217" t="n">
+        <v>13760302992</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr"/>
@@ -11384,6 +12682,14 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="L217" t="n">
+        <v>665.9400000000001</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11391,10 +12697,8 @@
           <t>曹霞平</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>13841379772</t>
-        </is>
+      <c r="B218" t="n">
+        <v>13841379772</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
@@ -11435,6 +12739,14 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="L218" t="n">
+        <v>704.8</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11442,10 +12754,8 @@
           <t>吕涛娜</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>15166210388</t>
-        </is>
+      <c r="B219" t="n">
+        <v>15166210388</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -11482,6 +12792,14 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="L219" t="n">
+        <v>238.94</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11489,10 +12807,8 @@
           <t>冯霞伟</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>13668650863</t>
-        </is>
+      <c r="B220" t="n">
+        <v>13668650863</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -11537,6 +12853,14 @@
           <t>2024-09-01</t>
         </is>
       </c>
+      <c r="L220" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11544,10 +12868,8 @@
           <t>韩娜</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>18764300981</t>
-        </is>
+      <c r="B221" t="n">
+        <v>18764300981</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -11588,6 +12910,14 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="L221" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11595,10 +12925,8 @@
           <t>朱军娟</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>18859463688</t>
-        </is>
+      <c r="B222" t="n">
+        <v>18859463688</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -11635,6 +12963,14 @@
           <t>2024-07-22</t>
         </is>
       </c>
+      <c r="L222" t="n">
+        <v>655.71</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11642,10 +12978,8 @@
           <t>冯刚</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>15172138658</t>
-        </is>
+      <c r="B223" t="n">
+        <v>15172138658</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -11686,6 +13020,14 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="L223" t="n">
+        <v>212.58</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11693,10 +13035,8 @@
           <t>华娜</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>15151906698</t>
-        </is>
+      <c r="B224" t="n">
+        <v>15151906698</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr"/>
@@ -11733,6 +13073,14 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="L224" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11740,10 +13088,8 @@
           <t>尤强</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>18888392053</t>
-        </is>
+      <c r="B225" t="n">
+        <v>18888392053</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -11784,6 +13130,14 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="L225" t="n">
+        <v>370.73</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11791,10 +13145,8 @@
           <t>赵英娜</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>18748955439</t>
-        </is>
+      <c r="B226" t="n">
+        <v>18748955439</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -11835,6 +13187,14 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="L226" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11842,10 +13202,8 @@
           <t>尤勇华</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>18748947697</t>
-        </is>
+      <c r="B227" t="n">
+        <v>18748947697</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -11890,6 +13248,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="L227" t="n">
+        <v>520.73</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11897,10 +13263,8 @@
           <t>韩刚华</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>15865880434</t>
-        </is>
+      <c r="B228" t="n">
+        <v>15865880434</v>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr"/>
@@ -11933,6 +13297,14 @@
           <t>2024-04-21</t>
         </is>
       </c>
+      <c r="L228" t="n">
+        <v>719.42</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11940,10 +13312,8 @@
           <t>秦丽刚</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>15173334333</t>
-        </is>
+      <c r="B229" t="n">
+        <v>15173334333</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -11988,6 +13358,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="L229" t="n">
+        <v>220.8</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11995,10 +13373,8 @@
           <t>孙明</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>15879472846</t>
-        </is>
+      <c r="B230" t="n">
+        <v>15879472846</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
@@ -12031,6 +13407,14 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="L230" t="n">
+        <v>766.3200000000001</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12038,10 +13422,8 @@
           <t>施杰文</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>15071875003</t>
-        </is>
+      <c r="B231" t="n">
+        <v>15071875003</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -12082,6 +13464,14 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="L231" t="n">
+        <v>674.71</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12089,10 +13479,8 @@
           <t>吕艳</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>15936556472</t>
-        </is>
+      <c r="B232" t="n">
+        <v>15936556472</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -12137,6 +13525,14 @@
           <t>2024-04-10</t>
         </is>
       </c>
+      <c r="L232" t="n">
+        <v>415.04</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12144,10 +13540,8 @@
           <t>陈华静</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>18602672885</t>
-        </is>
+      <c r="B233" t="n">
+        <v>18602672885</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -12184,6 +13578,14 @@
           <t>2024-08-31</t>
         </is>
       </c>
+      <c r="L233" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12191,10 +13593,8 @@
           <t>郑涛军</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>15858845061</t>
-        </is>
+      <c r="B234" t="n">
+        <v>15858845061</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -12235,6 +13635,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="L234" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12242,10 +13650,8 @@
           <t>姜文娜</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>15994722569</t>
-        </is>
+      <c r="B235" t="n">
+        <v>15994722569</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -12286,6 +13692,14 @@
           <t>2024-05-29</t>
         </is>
       </c>
+      <c r="L235" t="n">
+        <v>404.39</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12293,10 +13707,8 @@
           <t>秦霞军</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>18659876220</t>
-        </is>
+      <c r="B236" t="n">
+        <v>18659876220</v>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
@@ -12337,6 +13749,14 @@
           <t>2024-02-18</t>
         </is>
       </c>
+      <c r="L236" t="n">
+        <v>240.92</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12344,10 +13764,8 @@
           <t>周明伟</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>13668114921</t>
-        </is>
+      <c r="B237" t="n">
+        <v>13668114921</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -12392,6 +13810,14 @@
           <t>2024-01-15</t>
         </is>
       </c>
+      <c r="L237" t="n">
+        <v>325.41</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12399,10 +13825,8 @@
           <t>孙刚</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>15877848728</t>
-        </is>
+      <c r="B238" t="n">
+        <v>15877848728</v>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
@@ -12439,6 +13863,14 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="L238" t="n">
+        <v>446.02</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12446,10 +13878,8 @@
           <t>韩华</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>15256424008</t>
-        </is>
+      <c r="B239" t="n">
+        <v>15256424008</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -12490,6 +13920,14 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="L239" t="n">
+        <v>447.6</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12497,10 +13935,8 @@
           <t>赵文</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>15293085368</t>
-        </is>
+      <c r="B240" t="n">
+        <v>15293085368</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -12541,6 +13977,14 @@
           <t>2024-05-02</t>
         </is>
       </c>
+      <c r="L240" t="n">
+        <v>267.63</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12548,10 +13992,8 @@
           <t>秦洋秀</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>13646312241</t>
-        </is>
+      <c r="B241" t="n">
+        <v>13646312241</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -12592,6 +14034,14 @@
           <t>2024-01-12</t>
         </is>
       </c>
+      <c r="L241" t="n">
+        <v>386.62</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12599,10 +14049,8 @@
           <t>卫敏</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>15070312073</t>
-        </is>
+      <c r="B242" t="n">
+        <v>15070312073</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -12643,6 +14091,14 @@
           <t>2024-01-29</t>
         </is>
       </c>
+      <c r="L242" t="n">
+        <v>504.98</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12650,10 +14106,8 @@
           <t>秦文</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>18772346013</t>
-        </is>
+      <c r="B243" t="n">
+        <v>18772346013</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -12690,6 +14144,14 @@
           <t>2024-12-14</t>
         </is>
       </c>
+      <c r="L243" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12697,10 +14159,8 @@
           <t>许勇</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>13508814743</t>
-        </is>
+      <c r="B244" t="n">
+        <v>13508814743</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -12741,6 +14201,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="L244" t="n">
+        <v>772.38</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12748,10 +14216,8 @@
           <t>王杰伟</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>13897925132</t>
-        </is>
+      <c r="B245" t="n">
+        <v>13897925132</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -12792,6 +14258,14 @@
           <t>2024-04-29</t>
         </is>
       </c>
+      <c r="L245" t="n">
+        <v>217.65</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12799,10 +14273,8 @@
           <t>何秀文</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>15873065240</t>
-        </is>
+      <c r="B246" t="n">
+        <v>15873065240</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -12847,6 +14319,14 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="L246" t="n">
+        <v>170.03</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12854,10 +14334,8 @@
           <t>秦霞秀</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>15018274485</t>
-        </is>
+      <c r="B247" t="n">
+        <v>15018274485</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -12898,6 +14376,14 @@
           <t>2024-02-02</t>
         </is>
       </c>
+      <c r="L247" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12905,10 +14391,8 @@
           <t>孔强明</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>13682945651</t>
-        </is>
+      <c r="B248" t="n">
+        <v>13682945651</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
@@ -12941,6 +14425,14 @@
           <t>2024-04-13</t>
         </is>
       </c>
+      <c r="L248" t="n">
+        <v>237.59</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12948,10 +14440,8 @@
           <t>郑明</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>13896789940</t>
-        </is>
+      <c r="B249" t="n">
+        <v>13896789940</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -12996,6 +14486,14 @@
           <t>2024-02-01</t>
         </is>
       </c>
+      <c r="L249" t="n">
+        <v>220.46</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13003,10 +14501,8 @@
           <t>张秀娟</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>13750948014</t>
-        </is>
+      <c r="B250" t="n">
+        <v>13750948014</v>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
@@ -13043,6 +14539,14 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="L250" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13050,10 +14554,8 @@
           <t>杨兰丽</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>18786195761</t>
-        </is>
+      <c r="B251" t="n">
+        <v>18786195761</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
@@ -13090,6 +14592,14 @@
           <t>2024-08-14</t>
         </is>
       </c>
+      <c r="L251" t="n">
+        <v>362.78</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13097,10 +14607,8 @@
           <t>施勇勇</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>13756659398</t>
-        </is>
+      <c r="B252" t="n">
+        <v>13756659398</v>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr"/>
@@ -13133,6 +14641,14 @@
           <t>2024-01-18</t>
         </is>
       </c>
+      <c r="L252" t="n">
+        <v>759.61</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13140,10 +14656,8 @@
           <t>尤霞</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>15040433504</t>
-        </is>
+      <c r="B253" t="n">
+        <v>15040433504</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -13180,6 +14694,14 @@
           <t>2024-05-15</t>
         </is>
       </c>
+      <c r="L253" t="n">
+        <v>423.39</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13187,10 +14709,8 @@
           <t>张兰</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>15241969315</t>
-        </is>
+      <c r="B254" t="n">
+        <v>15241969315</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -13231,6 +14751,14 @@
           <t>2024-06-20</t>
         </is>
       </c>
+      <c r="L254" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13238,10 +14766,8 @@
           <t>施娟</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>13713906048</t>
-        </is>
+      <c r="B255" t="n">
+        <v>13713906048</v>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
@@ -13274,6 +14800,14 @@
           <t>2024-07-20</t>
         </is>
       </c>
+      <c r="L255" t="n">
+        <v>437.46</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13281,10 +14815,8 @@
           <t>金文超</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>13936462251</t>
-        </is>
+      <c r="B256" t="n">
+        <v>13936462251</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -13321,6 +14853,14 @@
           <t>2024-03-07</t>
         </is>
       </c>
+      <c r="L256" t="n">
+        <v>675.73</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13328,10 +14868,8 @@
           <t>冯明明</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>15993898331</t>
-        </is>
+      <c r="B257" t="n">
+        <v>15993898331</v>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
@@ -13372,6 +14910,14 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="L257" t="n">
+        <v>126.93</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13379,10 +14925,8 @@
           <t>张艳</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>15890425979</t>
-        </is>
+      <c r="B258" t="n">
+        <v>15890425979</v>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
@@ -13419,6 +14963,14 @@
           <t>2024-02-13</t>
         </is>
       </c>
+      <c r="L258" t="n">
+        <v>743.73</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13426,10 +14978,8 @@
           <t>王英</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>18824051477</t>
-        </is>
+      <c r="B259" t="n">
+        <v>18824051477</v>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
@@ -13466,6 +15016,14 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="L259" t="n">
+        <v>566.48</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13473,10 +15031,8 @@
           <t>陈桂伟</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>15998042043</t>
-        </is>
+      <c r="B260" t="n">
+        <v>15998042043</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -13521,6 +15077,14 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="L260" t="n">
+        <v>424.25</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13528,10 +15092,8 @@
           <t>张敏</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>13763681579</t>
-        </is>
+      <c r="B261" t="n">
+        <v>13763681579</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -13572,6 +15134,14 @@
           <t>2024-06-19</t>
         </is>
       </c>
+      <c r="L261" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13579,10 +15149,8 @@
           <t>姜杰伟</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>15855438404</t>
-        </is>
+      <c r="B262" t="n">
+        <v>15855438404</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -13619,6 +15187,14 @@
           <t>2024-02-14</t>
         </is>
       </c>
+      <c r="L262" t="n">
+        <v>574.4299999999999</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13626,10 +15202,8 @@
           <t>孔超霞</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>13736392649</t>
-        </is>
+      <c r="B263" t="n">
+        <v>13736392649</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -13674,6 +15248,14 @@
           <t>2024-09-25</t>
         </is>
       </c>
+      <c r="L263" t="n">
+        <v>155.44</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13681,10 +15263,8 @@
           <t>冯娟文</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>15092518812</t>
-        </is>
+      <c r="B264" t="n">
+        <v>15092518812</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -13729,6 +15309,14 @@
           <t>2024-11-22</t>
         </is>
       </c>
+      <c r="L264" t="n">
+        <v>780.88</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13736,10 +15324,8 @@
           <t>秦静敏</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>15020994999</t>
-        </is>
+      <c r="B265" t="n">
+        <v>15020994999</v>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
@@ -13780,6 +15366,14 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="L265" t="n">
+        <v>113.73</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13787,10 +15381,8 @@
           <t>陶桂丽</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>13767722330</t>
-        </is>
+      <c r="B266" t="n">
+        <v>13767722330</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -13831,6 +15423,14 @@
           <t>2024-08-12</t>
         </is>
       </c>
+      <c r="L266" t="n">
+        <v>565.59</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13838,10 +15438,8 @@
           <t>姜桂</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>18636609656</t>
-        </is>
+      <c r="B267" t="n">
+        <v>18636609656</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -13882,6 +15480,14 @@
           <t>2024-01-22</t>
         </is>
       </c>
+      <c r="L267" t="n">
+        <v>325.74</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13889,10 +15495,8 @@
           <t>杨超英</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>13886803476</t>
-        </is>
+      <c r="B268" t="n">
+        <v>13886803476</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -13933,6 +15537,14 @@
           <t>2024-03-13</t>
         </is>
       </c>
+      <c r="L268" t="n">
+        <v>742.6900000000001</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13940,10 +15552,8 @@
           <t>魏平</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>13581298266</t>
-        </is>
+      <c r="B269" t="n">
+        <v>13581298266</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -13988,6 +15598,14 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="L269" t="n">
+        <v>407.31</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13995,10 +15613,8 @@
           <t>褚桂娜</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>13975186892</t>
-        </is>
+      <c r="B270" t="n">
+        <v>13975186892</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -14043,6 +15659,14 @@
           <t>2024-01-27</t>
         </is>
       </c>
+      <c r="L270" t="n">
+        <v>422.33</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14050,10 +15674,8 @@
           <t>严洋</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>13674212309</t>
-        </is>
+      <c r="B271" t="n">
+        <v>13674212309</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -14098,6 +15720,14 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="L271" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14105,10 +15735,8 @@
           <t>陶涛</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>13999038498</t>
-        </is>
+      <c r="B272" t="n">
+        <v>13999038498</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -14149,6 +15777,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="L272" t="n">
+        <v>514.5599999999999</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14156,10 +15792,8 @@
           <t>许勇芳</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>13962249998</t>
-        </is>
+      <c r="B273" t="n">
+        <v>13962249998</v>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
@@ -14200,6 +15834,14 @@
           <t>2024-02-04</t>
         </is>
       </c>
+      <c r="L273" t="n">
+        <v>494.04</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14207,10 +15849,8 @@
           <t>华秀</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>18621458683</t>
-        </is>
+      <c r="B274" t="n">
+        <v>18621458683</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -14255,6 +15895,14 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="L274" t="n">
+        <v>437.1</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14262,10 +15910,8 @@
           <t>施静明</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>18777293430</t>
-        </is>
+      <c r="B275" t="n">
+        <v>18777293430</v>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
@@ -14306,6 +15952,14 @@
           <t>2024-06-28</t>
         </is>
       </c>
+      <c r="L275" t="n">
+        <v>474.87</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14313,10 +15967,8 @@
           <t>沈伟桂</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>15241448850</t>
-        </is>
+      <c r="B276" t="n">
+        <v>15241448850</v>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
@@ -14353,6 +16005,14 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="L276" t="n">
+        <v>232.77</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14360,10 +16020,8 @@
           <t>陶明平</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>15072785760</t>
-        </is>
+      <c r="B277" t="n">
+        <v>15072785760</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -14404,6 +16062,14 @@
           <t>2024-02-03</t>
         </is>
       </c>
+      <c r="L277" t="n">
+        <v>350.76</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14411,10 +16077,8 @@
           <t>陈军勇</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>15982996291</t>
-        </is>
+      <c r="B278" t="n">
+        <v>15982996291</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -14455,6 +16119,14 @@
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="L278" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14462,10 +16134,8 @@
           <t>金洋</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>15221503178</t>
-        </is>
+      <c r="B279" t="n">
+        <v>15221503178</v>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
@@ -14502,6 +16172,14 @@
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="L279" t="n">
+        <v>613.22</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14509,10 +16187,8 @@
           <t>何静敏</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>13782307681</t>
-        </is>
+      <c r="B280" t="n">
+        <v>13782307681</v>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
@@ -14549,6 +16225,14 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="L280" t="n">
+        <v>678.85</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14556,10 +16240,8 @@
           <t>钱兰平</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>15153344857</t>
-        </is>
+      <c r="B281" t="n">
+        <v>15153344857</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -14600,6 +16282,14 @@
           <t>2024-06-28</t>
         </is>
       </c>
+      <c r="L281" t="n">
+        <v>425.6</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14607,10 +16297,8 @@
           <t>何军</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>13549321495</t>
-        </is>
+      <c r="B282" t="n">
+        <v>13549321495</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -14655,6 +16343,14 @@
           <t>2024-08-06</t>
         </is>
       </c>
+      <c r="L282" t="n">
+        <v>581.84</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14662,10 +16358,8 @@
           <t>曹丽兰</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>18979545381</t>
-        </is>
+      <c r="B283" t="n">
+        <v>18979545381</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -14706,6 +16400,14 @@
           <t>2024-12-16</t>
         </is>
       </c>
+      <c r="L283" t="n">
+        <v>667.64</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14713,10 +16415,8 @@
           <t>魏明</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>15129456255</t>
-        </is>
+      <c r="B284" t="n">
+        <v>15129456255</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -14757,6 +16457,14 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="L284" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14764,10 +16472,8 @@
           <t>冯超</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>13715814876</t>
-        </is>
+      <c r="B285" t="n">
+        <v>13715814876</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -14808,6 +16514,14 @@
           <t>2024-04-16</t>
         </is>
       </c>
+      <c r="L285" t="n">
+        <v>510.69</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14815,10 +16529,8 @@
           <t>华华兰</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>13658321971</t>
-        </is>
+      <c r="B286" t="n">
+        <v>13658321971</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -14859,6 +16571,14 @@
           <t>2024-02-25</t>
         </is>
       </c>
+      <c r="L286" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14866,10 +16586,8 @@
           <t>孔勇</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>18901329022</t>
-        </is>
+      <c r="B287" t="n">
+        <v>18901329022</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -14906,6 +16624,14 @@
           <t>2024-06-04</t>
         </is>
       </c>
+      <c r="L287" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14913,10 +16639,8 @@
           <t>华桂艳</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>13990986240</t>
-        </is>
+      <c r="B288" t="n">
+        <v>13990986240</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -14961,6 +16685,14 @@
           <t>2024-04-30</t>
         </is>
       </c>
+      <c r="L288" t="n">
+        <v>517.99</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14968,10 +16700,8 @@
           <t>华桂平</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>15866668327</t>
-        </is>
+      <c r="B289" t="n">
+        <v>15866668327</v>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr"/>
@@ -15008,6 +16738,14 @@
           <t>2024-03-05</t>
         </is>
       </c>
+      <c r="L289" t="n">
+        <v>418.54</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15015,10 +16753,8 @@
           <t>冯伟</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>13827621267</t>
-        </is>
+      <c r="B290" t="n">
+        <v>13827621267</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -15059,6 +16795,14 @@
           <t>2024-04-25</t>
         </is>
       </c>
+      <c r="L290" t="n">
+        <v>575.59</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15066,10 +16810,8 @@
           <t>卫娟兰</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>18638468950</t>
-        </is>
+      <c r="B291" t="n">
+        <v>18638468950</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -15106,6 +16848,14 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="L291" t="n">
+        <v>219.68</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15113,10 +16863,8 @@
           <t>秦涛超</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>18813718949</t>
-        </is>
+      <c r="B292" t="n">
+        <v>18813718949</v>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
@@ -15157,6 +16905,14 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="L292" t="n">
+        <v>596.52</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15164,10 +16920,8 @@
           <t>严艳华</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>15242094940</t>
-        </is>
+      <c r="B293" t="n">
+        <v>15242094940</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -15208,6 +16962,14 @@
           <t>2024-03-05</t>
         </is>
       </c>
+      <c r="L293" t="n">
+        <v>555.46</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15215,10 +16977,8 @@
           <t>周华</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>15094440192</t>
-        </is>
+      <c r="B294" t="n">
+        <v>15094440192</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -15255,6 +17015,14 @@
           <t>2024-04-30</t>
         </is>
       </c>
+      <c r="L294" t="n">
+        <v>189.39</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15262,10 +17030,8 @@
           <t>姜丽芳</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>15812927663</t>
-        </is>
+      <c r="B295" t="n">
+        <v>15812927663</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -15310,6 +17076,14 @@
           <t>2024-01-27</t>
         </is>
       </c>
+      <c r="L295" t="n">
+        <v>624.96</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15317,10 +17091,8 @@
           <t>褚涛</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>15278366742</t>
-        </is>
+      <c r="B296" t="n">
+        <v>15278366742</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -15361,6 +17133,14 @@
           <t>2024-11-22</t>
         </is>
       </c>
+      <c r="L296" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15368,10 +17148,8 @@
           <t>施娟平</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>13745441496</t>
-        </is>
+      <c r="B297" t="n">
+        <v>13745441496</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -15416,6 +17194,14 @@
           <t>2024-02-04</t>
         </is>
       </c>
+      <c r="L297" t="n">
+        <v>654.12</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15423,10 +17209,8 @@
           <t>赵娟</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>13975344300</t>
-        </is>
+      <c r="B298" t="n">
+        <v>13975344300</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -15467,6 +17251,14 @@
           <t>2024-03-07</t>
         </is>
       </c>
+      <c r="L298" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15474,10 +17266,8 @@
           <t>孔刚平</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>18821244717</t>
-        </is>
+      <c r="B299" t="n">
+        <v>18821244717</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -15518,6 +17308,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="L299" t="n">
+        <v>253.85</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15525,10 +17323,8 @@
           <t>孔勇军</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>13742717396</t>
-        </is>
+      <c r="B300" t="n">
+        <v>13742717396</v>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
@@ -15565,6 +17361,14 @@
           <t>2024-02-24</t>
         </is>
       </c>
+      <c r="L300" t="n">
+        <v>673</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15572,10 +17376,8 @@
           <t>金桂</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>13811947072</t>
-        </is>
+      <c r="B301" t="n">
+        <v>13811947072</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -15616,6 +17418,14 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="L301" t="n">
+        <v>440.94</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15623,10 +17433,8 @@
           <t>王伟磊</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>15121819600</t>
-        </is>
+      <c r="B302" t="n">
+        <v>15121819600</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
@@ -15667,6 +17475,14 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="L302" t="n">
+        <v>316.56</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15674,10 +17490,8 @@
           <t>秦华文</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>13626542351</t>
-        </is>
+      <c r="B303" t="n">
+        <v>13626542351</v>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
@@ -15718,6 +17532,14 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="L303" t="n">
+        <v>483.96</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15725,10 +17547,8 @@
           <t>吴秀</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>18995931034</t>
-        </is>
+      <c r="B304" t="n">
+        <v>18995931034</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -15769,6 +17589,14 @@
           <t>2024-04-17</t>
         </is>
       </c>
+      <c r="L304" t="n">
+        <v>729.45</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15776,10 +17604,8 @@
           <t>秦桂平</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>13992832764</t>
-        </is>
+      <c r="B305" t="n">
+        <v>13992832764</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -15820,6 +17646,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="L305" t="n">
+        <v>134.06</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15827,10 +17661,8 @@
           <t>秦娜</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>18853767242</t>
-        </is>
+      <c r="B306" t="n">
+        <v>18853767242</v>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr"/>
@@ -15863,6 +17695,14 @@
           <t>2024-03-11</t>
         </is>
       </c>
+      <c r="L306" t="n">
+        <v>787.15</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15870,10 +17710,8 @@
           <t>姜娜敏</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>15026916697</t>
-        </is>
+      <c r="B307" t="n">
+        <v>15026916697</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -15918,6 +17756,14 @@
           <t>2024-08-10</t>
         </is>
       </c>
+      <c r="L307" t="n">
+        <v>230.12</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15925,10 +17771,8 @@
           <t>褚涛</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>13548281489</t>
-        </is>
+      <c r="B308" t="n">
+        <v>13548281489</v>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
@@ -15969,6 +17813,14 @@
           <t>2024-02-27</t>
         </is>
       </c>
+      <c r="L308" t="n">
+        <v>471.06</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15976,10 +17828,8 @@
           <t>张华</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>13839117182</t>
-        </is>
+      <c r="B309" t="n">
+        <v>13839117182</v>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
@@ -16016,6 +17866,14 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="L309" t="n">
+        <v>754.54</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16023,10 +17881,8 @@
           <t>蒋桂</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>18957871331</t>
-        </is>
+      <c r="B310" t="n">
+        <v>18957871331</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -16067,6 +17923,14 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="L310" t="n">
+        <v>689.21</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16074,10 +17938,8 @@
           <t>周超</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>18973829973</t>
-        </is>
+      <c r="B311" t="n">
+        <v>18973829973</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -16118,6 +17980,14 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="L311" t="n">
+        <v>710.98</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16125,10 +17995,8 @@
           <t>李刚平</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>13906513338</t>
-        </is>
+      <c r="B312" t="n">
+        <v>13906513338</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -16169,6 +18037,14 @@
           <t>2024-02-20</t>
         </is>
       </c>
+      <c r="L312" t="n">
+        <v>507</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -16176,10 +18052,8 @@
           <t>李平伟</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>13932677360</t>
-        </is>
+      <c r="B313" t="n">
+        <v>13932677360</v>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
@@ -16216,6 +18090,14 @@
           <t>2024-10-11</t>
         </is>
       </c>
+      <c r="L313" t="n">
+        <v>604.96</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -16223,10 +18105,8 @@
           <t>姜静</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>15109805009</t>
-        </is>
+      <c r="B314" t="n">
+        <v>15109805009</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -16271,6 +18151,14 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="L314" t="n">
+        <v>782.63</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -16278,10 +18166,8 @@
           <t>杨杰</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>18839909169</t>
-        </is>
+      <c r="B315" t="n">
+        <v>18839909169</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -16326,6 +18212,14 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="L315" t="n">
+        <v>237.53</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -16333,10 +18227,8 @@
           <t>许涛</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>13610799118</t>
-        </is>
+      <c r="B316" t="n">
+        <v>13610799118</v>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
@@ -16377,6 +18269,14 @@
           <t>2024-08-12</t>
         </is>
       </c>
+      <c r="L316" t="n">
+        <v>733.3099999999999</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -16384,10 +18284,8 @@
           <t>许霞华</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>18980841241</t>
-        </is>
+      <c r="B317" t="n">
+        <v>18980841241</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -16428,6 +18326,14 @@
           <t>2024-11-20</t>
         </is>
       </c>
+      <c r="L317" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -16435,10 +18341,8 @@
           <t>朱超</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>13701640052</t>
-        </is>
+      <c r="B318" t="n">
+        <v>13701640052</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -16479,6 +18383,14 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="L318" t="n">
+        <v>457.22</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -16486,10 +18398,8 @@
           <t>陈秀</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>15898262045</t>
-        </is>
+      <c r="B319" t="n">
+        <v>15898262045</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -16530,6 +18440,14 @@
           <t>2024-07-27</t>
         </is>
       </c>
+      <c r="L319" t="n">
+        <v>409.71</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -16537,10 +18455,8 @@
           <t>陈磊华</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>13626025634</t>
-        </is>
+      <c r="B320" t="n">
+        <v>13626025634</v>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr"/>
@@ -16573,6 +18489,14 @@
           <t>2024-08-23</t>
         </is>
       </c>
+      <c r="L320" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -16580,10 +18504,8 @@
           <t>施洋磊</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>15103654145</t>
-        </is>
+      <c r="B321" t="n">
+        <v>15103654145</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -16622,6 +18544,14 @@
       <c r="K321" t="inlineStr">
         <is>
           <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="L321" t="n">
+        <v>127.77</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>常规投放</t>
         </is>
       </c>
     </row>
